--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7377049180327869</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5845070422535211</v>
+        <v>0.676056338028169</v>
       </c>
       <c r="D2">
-        <v>0.5673076923076923</v>
+        <v>0.4181818181818182</v>
       </c>
       <c r="E2">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8421052631578947</v>
+        <v>0.8356164383561644</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.676056338028169</v>
+        <v>0.6690140845070423</v>
       </c>
       <c r="D2">
-        <v>0.4181818181818182</v>
+        <v>0.4351851851851852</v>
       </c>
       <c r="E2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F2">
+        <v>35</v>
+      </c>
+      <c r="G2">
         <v>34</v>
-      </c>
-      <c r="G2">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
